--- a/data/processed/harmonization/Carbon__Particulate_organic_matter_carbon/harmonized.xlsx
+++ b/data/processed/harmonization/Carbon__Particulate_organic_matter_carbon/harmonized.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="43" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:18</t>
+          <t>ER-MCB1:30:18</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:44</t>
+          <t>ER-MCB1:30:44</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:60</t>
+          <t>ER-MCB1:30:60</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:31</t>
+          <t>ER-MCB2:30:31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:36</t>
+          <t>ER-MCB2:30:36</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:43</t>
+          <t>ER-MCB2:30:43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:20</t>
+          <t>ER-MCB3:30:20</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:21</t>
+          <t>ER-MCB3:30:21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:25</t>
+          <t>ER-MCB3:30:25</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:28</t>
+          <t>ER-MCB1:70:28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:49</t>
+          <t>ER-MCB1:70:49</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB1:65</t>
+          <t>ER-MCB1:70:65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:46</t>
+          <t>ER-MCB2:70:46</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:50</t>
+          <t>ER-MCB2:70:50</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB2:52</t>
+          <t>ER-MCB2:70:52</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:17</t>
+          <t>ER-MCB3:70:17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:27</t>
+          <t>ER-MCB3:70:27</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ER-MCB3:55</t>
+          <t>ER-MCB3:70:55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>location:ID</t>
+          <t>location:depth:ID</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Control:2</t>
+          <t>Control:1:80-90</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Control:6</t>
+          <t>Control:1:40-50</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Control:9</t>
+          <t>Control:1:10-20</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Warmed:12</t>
+          <t>Warmed:2:80-90</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Warmed:16</t>
+          <t>Warmed:2:40-50</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Warmed:19</t>
+          <t>Warmed:2:10-20</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Control:22</t>
+          <t>Control:3:80-90</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Control:26</t>
+          <t>Control:3:40-50</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Control:29</t>
+          <t>Control:3:10-20</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Warmed:32</t>
+          <t>Warmed:4:80-90</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Warmed:36</t>
+          <t>Warmed:4:40-50</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Warmed:39</t>
+          <t>Warmed:4:10-20</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Control:42</t>
+          <t>Control:5:80-90</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Control:46</t>
+          <t>Control:5:40-50</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Control:49</t>
+          <t>Control:5:10-20</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Warmed:52</t>
+          <t>Warmed:6:80-90</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Warmed:56</t>
+          <t>Warmed:6:40-50</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Warmed:59</t>
+          <t>Warmed:6:10-20</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Control:2</t>
+          <t>Control:1:80-90</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Control:6</t>
+          <t>Control:1:40-50</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Control:9</t>
+          <t>Control:1:10-20</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Warmed:12</t>
+          <t>Warmed:2:80-90</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Warmed:16</t>
+          <t>Warmed:2:40-50</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Warmed:19</t>
+          <t>Warmed:2:10-20</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Control:22</t>
+          <t>Control:3:80-90</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Control:26</t>
+          <t>Control:3:40-50</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Control:29</t>
+          <t>Control:3:10-20</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Warmed:32</t>
+          <t>Warmed:4:80-90</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Warmed:36</t>
+          <t>Warmed:4:40-50</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Warmed:39</t>
+          <t>Warmed:4:10-20</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Control:42</t>
+          <t>Control:5:80-90</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Control:46</t>
+          <t>Control:5:40-50</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Control:49</t>
+          <t>Control:5:10-20</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Warmed:52</t>
+          <t>Warmed:6:80-90</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Warmed:56</t>
+          <t>Warmed:6:40-50</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Warmed:59</t>
+          <t>Warmed:6:10-20</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Control:2</t>
+          <t>Control:1:80-90</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Control:6</t>
+          <t>Control:1:40-50</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Control:9</t>
+          <t>Control:1:10-20</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Warmed:12</t>
+          <t>Warmed:2:80-90</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Warmed:16</t>
+          <t>Warmed:2:40-50</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Warmed:19</t>
+          <t>Warmed:2:10-20</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Control:22</t>
+          <t>Control:3:80-90</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Control:26</t>
+          <t>Control:3:40-50</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Control:29</t>
+          <t>Control:3:10-20</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Warmed:32</t>
+          <t>Warmed:4:80-90</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Warmed:36</t>
+          <t>Warmed:4:40-50</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Warmed:39</t>
+          <t>Warmed:4:10-20</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Control:42</t>
+          <t>Control:5:80-90</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Control:46</t>
+          <t>Control:5:40-50</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Control:49</t>
+          <t>Control:5:10-20</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3902,12 +3902,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Warmed:52</t>
+          <t>Warmed:6:80-90</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Warmed:56</t>
+          <t>Warmed:6:40-50</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Warmed:59</t>
+          <t>Warmed:6:10-20</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Control:2</t>
+          <t>Control:1:80-90</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Control:6</t>
+          <t>Control:1:40-50</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Control:9</t>
+          <t>Control:1:10-20</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Warmed:12</t>
+          <t>Warmed:2:80-90</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Warmed:16</t>
+          <t>Warmed:2:40-50</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Warmed:19</t>
+          <t>Warmed:2:10-20</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Control:22</t>
+          <t>Control:3:80-90</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Control:26</t>
+          <t>Control:3:40-50</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Control:29</t>
+          <t>Control:3:10-20</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4478,12 +4478,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Warmed:32</t>
+          <t>Warmed:4:80-90</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Warmed:36</t>
+          <t>Warmed:4:40-50</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Warmed:39</t>
+          <t>Warmed:4:10-20</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Control:42</t>
+          <t>Control:5:80-90</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Control:46</t>
+          <t>Control:5:40-50</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Control:49</t>
+          <t>Control:5:10-20</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Warmed:52</t>
+          <t>Warmed:6:80-90</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Warmed:56</t>
+          <t>Warmed:6:40-50</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Warmed:59</t>
+          <t>Warmed:6:10-20</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
